--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1293" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="186">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-14T06:15:19+00:00</t>
+    <t>2024-06-18T10:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -450,6 +450,22 @@
     <t>Dosaging and administration instructions</t>
   </si>
   <si>
+    <t>be-model-medicationprescription.dosageOverride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Element {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/BL}
+</t>
+  </si>
+  <si>
+    <t>Indication if standard dosage is overriden</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.dosageOverrideReason</t>
+  </si>
+  <si>
+    <t>Reason why standard dosage is overriden</t>
+  </si>
+  <si>
     <t>be-model-medicationprescription.validFrom</t>
   </si>
   <si>
@@ -557,10 +573,6 @@
   </si>
   <si>
     <t>be-model-medicationprescription.noSubstitution.noSubstitutionFlag</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Element {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/BL}
-</t>
   </si>
   <si>
     <t>Substitution of the product is not allowed.</t>
@@ -891,7 +903,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ40"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.22265625" customWidth="true" bestFit="true"/>
@@ -2875,7 +2887,7 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L20" t="s" s="2">
         <v>143</v>
@@ -2963,7 +2975,7 @@
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2975,13 +2987,13 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3038,7 +3050,7 @@
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>74</v>
@@ -3049,10 +3061,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3063,7 +3075,7 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3075,13 +3087,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3132,13 +3144,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3149,10 +3161,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3163,7 +3175,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3175,13 +3187,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3232,27 +3244,27 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3263,7 +3275,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3275,13 +3287,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3332,13 +3344,13 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>74</v>
@@ -3349,21 +3361,21 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3375,17 +3387,15 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -3422,75 +3432,71 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
@@ -3538,38 +3544,38 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
@@ -3581,15 +3587,17 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>154</v>
+        <v>116</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>155</v>
+        <v>117</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>74</v>
@@ -3626,71 +3634,75 @@
         <v>74</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>74</v>
       </c>
@@ -3738,27 +3750,27 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3781,7 +3793,7 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>160</v>
@@ -3838,7 +3850,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -3881,13 +3893,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3955,10 +3967,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3966,7 +3978,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>80</v>
@@ -3981,13 +3993,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4038,10 +4050,10 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
         <v>80</v>
@@ -4055,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4081,13 +4093,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4138,7 +4150,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4155,10 +4167,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4166,7 +4178,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>80</v>
@@ -4181,7 +4193,7 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>168</v>
+        <v>145</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>169</v>
@@ -4238,10 +4250,10 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>80</v>
@@ -4250,7 +4262,7 @@
         <v>74</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34">
@@ -4281,13 +4293,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>112</v>
+        <v>171</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4338,7 +4350,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>113</v>
+        <v>170</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4355,21 +4367,21 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4381,17 +4393,15 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>116</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>117</v>
+        <v>174</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>74</v>
@@ -4428,75 +4438,71 @@
         <v>74</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>126</v>
+        <v>74</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
@@ -4544,38 +4550,38 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>74</v>
+        <v>115</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4587,15 +4593,17 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4632,71 +4640,75 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>74</v>
+        <v>126</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>91</v>
+        <v>116</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>130</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -4744,19 +4756,19 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>176</v>
+        <v>131</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39">
@@ -4772,7 +4784,7 @@
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>80</v>
@@ -4787,7 +4799,7 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>96</v>
+        <v>140</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>179</v>
@@ -4847,7 +4859,7 @@
         <v>178</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>80</v>
@@ -4875,7 +4887,7 @@
         <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -4950,12 +4962,212 @@
         <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AI40" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:21+00:00</t>
+    <t>2024-06-18T10:57:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -336,6 +336,16 @@
   </si>
   <si>
     <t>Question: would we want to add basic Practicioner model?</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-organization)
+</t>
+  </si>
+  <si>
+    <t>The organization from which the prescriber issues the prescription.</t>
   </si>
   <si>
     <t>be-model-medicationprescription.indication</t>
@@ -903,7 +913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ42"/>
+  <dimension ref="A1:AJ43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.22265625" customWidth="true" bestFit="true"/>
@@ -1969,7 +1979,7 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
@@ -2044,21 +2054,21 @@
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2069,7 +2079,7 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2081,13 +2091,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>111</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2138,38 +2148,38 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2181,17 +2191,15 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
@@ -2228,43 +2236,43 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2277,26 +2285,24 @@
         <v>74</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
@@ -2332,19 +2338,19 @@
         <v>74</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2356,19 +2362,19 @@
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2381,22 +2387,26 @@
         <v>74</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O15" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2444,7 +2454,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2456,15 +2466,15 @@
         <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2490,10 +2500,10 @@
         <v>91</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2544,7 +2554,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2561,10 +2571,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2575,7 +2585,7 @@
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2587,13 +2597,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2644,13 +2654,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2661,10 +2671,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2672,7 +2682,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>80</v>
@@ -2687,7 +2697,7 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="L18" t="s" s="2">
         <v>138</v>
@@ -2744,10 +2754,10 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>80</v>
@@ -2772,7 +2782,7 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>80</v>
@@ -2847,7 +2857,7 @@
         <v>139</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>80</v>
@@ -2887,13 +2897,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2961,10 +2971,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2987,7 +2997,7 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="L21" t="s" s="2">
         <v>146</v>
@@ -3044,7 +3054,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3087,13 +3097,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3161,10 +3171,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3175,7 +3185,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3187,13 +3197,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3244,13 +3254,13 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3261,10 +3271,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3287,13 +3297,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3344,7 +3354,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3361,10 +3371,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3375,7 +3385,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3387,13 +3397,13 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3444,27 +3454,27 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3487,13 +3497,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>112</v>
+        <v>157</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3544,7 +3554,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3556,26 +3566,26 @@
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
@@ -3587,17 +3597,15 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>74</v>
@@ -3634,43 +3642,43 @@
         <v>74</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -3683,26 +3691,24 @@
         <v>74</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>74</v>
       </c>
@@ -3738,19 +3744,19 @@
         <v>74</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3762,47 +3768,51 @@
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>159</v>
+        <v>119</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>74</v>
       </c>
@@ -3850,19 +3860,19 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>158</v>
+        <v>134</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30">
@@ -3993,13 +4003,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>81</v>
+        <v>165</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4067,10 +4077,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4093,13 +4103,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>145</v>
+        <v>81</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4150,7 +4160,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4167,10 +4177,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4178,7 +4188,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>80</v>
@@ -4193,13 +4203,13 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4250,10 +4260,10 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>80</v>
@@ -4267,10 +4277,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4278,7 +4288,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>80</v>
@@ -4293,13 +4303,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4350,10 +4360,10 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -4367,10 +4377,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4393,7 +4403,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>173</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>174</v>
@@ -4450,7 +4460,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -4462,7 +4472,7 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>108</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36">
@@ -4493,13 +4503,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>110</v>
+        <v>176</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>112</v>
+        <v>177</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4550,7 +4560,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -4562,26 +4572,26 @@
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4593,17 +4603,15 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4640,43 +4648,43 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>120</v>
+        <v>74</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -4689,26 +4697,24 @@
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>130</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -4744,19 +4750,19 @@
         <v>74</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -4768,47 +4774,51 @@
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -4856,27 +4866,27 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>178</v>
+        <v>134</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4884,7 +4894,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>80</v>
@@ -4899,13 +4909,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4956,10 +4966,10 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>80</v>
@@ -4973,10 +4983,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -4999,13 +5009,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5056,7 +5066,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5073,10 +5083,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5087,7 +5097,7 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -5099,13 +5109,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5156,18 +5166,118 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G43" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AI42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="191">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:59+00:00</t>
+    <t>2024-06-18T10:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -537,6 +537,12 @@
   </si>
   <si>
     <t>Amount of medication to supply per dispense</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.instructionsForReimbursement</t>
+  </si>
+  <si>
+    <t>Instructions for reimbursement</t>
   </si>
   <si>
     <t>be-model-medicationprescription.groupIdentifier</t>
@@ -913,7 +919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AJ44"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.22265625" customWidth="true" bestFit="true"/>
@@ -2785,7 +2791,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2860,7 +2866,7 @@
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -4103,7 +4109,7 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>168</v>
@@ -4203,7 +4209,7 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>81</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>170</v>
@@ -4288,7 +4294,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>80</v>
@@ -4363,7 +4369,7 @@
         <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -4388,7 +4394,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>80</v>
@@ -4403,7 +4409,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>174</v>
@@ -4463,7 +4469,7 @@
         <v>173</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>80</v>
@@ -4503,13 +4509,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>177</v>
-      </c>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4572,15 +4578,15 @@
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4603,13 +4609,13 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>114</v>
+        <v>179</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4660,7 +4666,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -4672,26 +4678,26 @@
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
@@ -4703,17 +4709,15 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -4750,43 +4754,43 @@
         <v>74</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -4799,26 +4803,24 @@
         <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>119</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="O39" t="s" s="2">
-        <v>133</v>
-      </c>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -4854,19 +4856,19 @@
         <v>74</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -4883,42 +4885,46 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>74</v>
+        <v>129</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -4966,19 +4972,19 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>181</v>
+        <v>134</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41">
@@ -4994,7 +5000,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>80</v>
@@ -5009,7 +5015,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>184</v>
@@ -5069,7 +5075,7 @@
         <v>183</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>80</v>
@@ -5109,7 +5115,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>186</v>
@@ -5197,7 +5203,7 @@
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -5209,7 +5215,7 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>188</v>
@@ -5272,12 +5278,112 @@
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G44" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AI43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1417" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="189">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:58:59+00:00</t>
+    <t>2024-06-18T11:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -537,12 +537,6 @@
   </si>
   <si>
     <t>Amount of medication to supply per dispense</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.instructionsForReimbursement</t>
-  </si>
-  <si>
-    <t>Instructions for reimbursement</t>
   </si>
   <si>
     <t>be-model-medicationprescription.groupIdentifier</t>
@@ -919,7 +913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ44"/>
+  <dimension ref="A1:AJ43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.22265625" customWidth="true" bestFit="true"/>
@@ -4109,7 +4103,7 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>168</v>
@@ -4209,7 +4203,7 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>81</v>
+        <v>148</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>170</v>
@@ -4294,7 +4288,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>80</v>
@@ -4369,7 +4363,7 @@
         <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -4394,7 +4388,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>80</v>
@@ -4409,7 +4403,7 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>174</v>
@@ -4469,7 +4463,7 @@
         <v>173</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>80</v>
@@ -4509,13 +4503,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4578,15 +4572,15 @@
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4609,13 +4603,13 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>179</v>
+        <v>114</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>179</v>
+        <v>115</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4666,7 +4660,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>177</v>
+        <v>116</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -4678,26 +4672,26 @@
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>74</v>
@@ -4709,15 +4703,17 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -4754,43 +4750,43 @@
         <v>74</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -4803,24 +4799,26 @@
         <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>119</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="N39" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="O39" s="2"/>
+      <c r="O39" t="s" s="2">
+        <v>133</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -4856,19 +4854,19 @@
         <v>74</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -4885,46 +4883,42 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>131</v>
+        <v>182</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -4972,19 +4966,19 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
@@ -5000,7 +4994,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>80</v>
@@ -5015,7 +5009,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>184</v>
@@ -5075,7 +5069,7 @@
         <v>183</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>80</v>
@@ -5115,7 +5109,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>186</v>
@@ -5203,7 +5197,7 @@
         <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>74</v>
@@ -5215,7 +5209,7 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>188</v>
@@ -5278,112 +5272,12 @@
         <v>75</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="187">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T11:16:13+00:00</t>
+    <t>2024-07-02T10:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(WORK))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -299,154 +299,142 @@
     <t>Status of the prescription, this should not be status of treatment</t>
   </si>
   <si>
-    <t>be-model-medicationprescription.statusReason</t>
-  </si>
-  <si>
-    <t>Reason for the current status of prescription, for example the reason why the prescription was made invalid</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.statusReasonText</t>
+    <t>be-model-medicationprescription.medication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/be-model-medication)
+</t>
+  </si>
+  <si>
+    <t>Prescribed product, branded, generic, virtual, extemporaneous, etc</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.prescriber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+</t>
+  </si>
+  <si>
+    <t>The person who made the prescription, and who takes the responsibility of the treatment</t>
+  </si>
+  <si>
+    <t>Question: would we want to add basic Practicioner model?</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.organization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-organization)
+</t>
+  </si>
+  <si>
+    <t>The organization from which the prescriber issues the prescription.</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/Class}
+</t>
+  </si>
+  <si>
+    <t>Reason for the prescription (typically diagnosis, or a procedure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication.extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication.reference</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication.code</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.indication.text</t>
   </si>
   <si>
     <t xml:space="preserve">Element {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/ST}
 </t>
   </si>
   <si>
-    <t>Textual reason for the current status of prescription</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.medication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/be-model-medication)
-</t>
-  </si>
-  <si>
-    <t>Prescribed product, branded, generic, virtual, extemporaneous, etc</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.prescriber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
-</t>
-  </si>
-  <si>
-    <t>The person who made the prescription, and who takes the responsibility of the treatment</t>
-  </si>
-  <si>
-    <t>Question: would we want to add basic Practicioner model?</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.organization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://www.ehealth.fgov.be/standards/fhir/core/StructureDefinition/be-organization)
-</t>
-  </si>
-  <si>
-    <t>The organization from which the prescriber issues the prescription.</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement {https://www.ehealth.fgov.be/standards/fhir/medication/StructureDefinition/Class}
-</t>
-  </si>
-  <si>
-    <t>Reason for the prescription (typically diagnosis, or a procedure)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication.extension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication.reference</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication.code</t>
-  </si>
-  <si>
-    <t>be-model-medicationprescription.indication.text</t>
-  </si>
-  <si>
     <t>Reason for the prescription in textual form. This might not be allowed by some implementations.</t>
   </si>
   <si>
@@ -537,6 +525,12 @@
   </si>
   <si>
     <t>Amount of medication to supply per dispense</t>
+  </si>
+  <si>
+    <t>be-model-medicationprescription.instructionsForReimbursement</t>
+  </si>
+  <si>
+    <t>Instructions for reimbursement</t>
   </si>
   <si>
     <t>be-model-medicationprescription.groupIdentifier</t>
@@ -913,7 +907,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ43"/>
+  <dimension ref="A1:AJ42"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="70.22265625" customWidth="true" bestFit="true"/>
@@ -1576,10 +1570,10 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>74</v>
@@ -1591,13 +1585,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1651,10 +1645,10 @@
         <v>93</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>74</v>
@@ -1665,10 +1659,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1676,7 +1670,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>80</v>
@@ -1691,13 +1685,13 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1748,10 +1742,10 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>80</v>
@@ -1765,10 +1759,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1776,7 +1770,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>80</v>
@@ -1791,13 +1785,13 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1848,10 +1842,10 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH9" t="s" s="2">
         <v>80</v>
@@ -1865,10 +1859,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1876,10 +1870,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>74</v>
@@ -1891,13 +1885,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1948,27 +1942,27 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1991,13 +1985,13 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2048,7 +2042,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2065,14 +2059,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2091,15 +2085,17 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N12" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N12" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>74</v>
@@ -2136,19 +2132,19 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2160,47 +2156,51 @@
         <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O13" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
@@ -2248,31 +2248,31 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2291,17 +2291,15 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
@@ -2338,19 +2336,19 @@
         <v>74</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2362,19 +2360,19 @@
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -2387,26 +2385,22 @@
         <v>74</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>105</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2454,7 +2448,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2466,15 +2460,15 @@
         <v>74</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2485,7 +2479,7 @@
         <v>75</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>74</v>
@@ -2497,13 +2491,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>110</v>
+        <v>134</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2554,13 +2548,13 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>74</v>
@@ -2571,10 +2565,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2582,7 +2576,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>76</v>
@@ -2597,13 +2591,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>91</v>
+        <v>136</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2654,10 +2648,10 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>76</v>
@@ -2671,10 +2665,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2697,13 +2691,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>96</v>
+        <v>139</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2754,7 +2748,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2771,10 +2765,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2782,10 +2776,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2797,13 +2791,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2854,13 +2848,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2871,10 +2865,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2897,13 +2891,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2954,7 +2948,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -2971,10 +2965,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2997,13 +2991,13 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3054,7 +3048,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3071,10 +3065,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3085,7 +3079,7 @@
         <v>75</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3097,7 +3091,7 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c r="L22" t="s" s="2">
         <v>149</v>
@@ -3154,13 +3148,13 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>74</v>
@@ -3185,7 +3179,7 @@
         <v>75</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3197,7 +3191,7 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L23" t="s" s="2">
         <v>151</v>
@@ -3260,7 +3254,7 @@
         <v>75</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>74</v>
@@ -3285,7 +3279,7 @@
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3297,7 +3291,7 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="L24" t="s" s="2">
         <v>153</v>
@@ -3360,13 +3354,13 @@
         <v>75</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -3385,7 +3379,7 @@
         <v>75</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>74</v>
@@ -3397,13 +3391,13 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>109</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3454,13 +3448,13 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
@@ -3471,21 +3465,21 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3497,15 +3491,17 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>157</v>
+        <v>115</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
@@ -3542,71 +3538,75 @@
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>111</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
+        <v>127</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>74</v>
       </c>
@@ -3654,38 +3654,38 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3697,17 +3697,15 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>119</v>
+        <v>158</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>122</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>74</v>
@@ -3744,31 +3742,31 @@
         <v>74</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29">
@@ -3780,39 +3778,35 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>74</v>
       </c>
@@ -3860,27 +3854,27 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3903,13 +3897,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3960,7 +3954,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -3977,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4003,7 +3997,7 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>165</v>
+        <v>81</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>166</v>
@@ -4060,7 +4054,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4103,7 +4097,7 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>81</v>
+        <v>144</v>
       </c>
       <c r="L32" t="s" s="2">
         <v>168</v>
@@ -4188,7 +4182,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>80</v>
@@ -4203,7 +4197,7 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>170</v>
@@ -4263,7 +4257,7 @@
         <v>169</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>80</v>
@@ -4288,7 +4282,7 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>80</v>
@@ -4303,7 +4297,7 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>172</v>
@@ -4363,7 +4357,7 @@
         <v>171</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>80</v>
@@ -4403,13 +4397,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4472,15 +4466,15 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>74</v>
+        <v>106</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4503,13 +4497,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4560,7 +4554,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -4572,26 +4566,26 @@
         <v>74</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>111</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>74</v>
+        <v>113</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>74</v>
@@ -4603,15 +4597,17 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
@@ -4648,43 +4644,43 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>74</v>
+        <v>119</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>74</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -4697,24 +4693,26 @@
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O38" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>128</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
       </c>
@@ -4750,19 +4748,19 @@
         <v>74</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -4774,51 +4772,47 @@
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>131</v>
+        <v>180</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>74</v>
       </c>
@@ -4866,19 +4860,19 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40">
@@ -4894,7 +4888,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>80</v>
@@ -4909,7 +4903,7 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>182</v>
@@ -4969,7 +4963,7 @@
         <v>181</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>80</v>
@@ -5009,7 +5003,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>184</v>
@@ -5097,7 +5091,7 @@
         <v>75</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>74</v>
@@ -5109,7 +5103,7 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="L42" t="s" s="2">
         <v>186</v>
@@ -5172,112 +5166,12 @@
         <v>75</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="188">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T10:09:21+00:00</t>
+    <t>2024-09-06T16:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -286,9 +286,6 @@
     <t>The person for whom the medication is prescribed/ordered</t>
   </si>
   <si>
-    <t>Question: would we want to add basic Patient model?</t>
-  </si>
-  <si>
     <t>be-model-medicationprescription.status</t>
   </si>
   <si>
@@ -495,7 +492,7 @@
     <t>be-model-medicationprescription.dispenseRequest</t>
   </si>
   <si>
-    <t>Dispense Request oir authorization for the prescribed medication</t>
+    <t>Dispense Request or authorization for the prescribed medication</t>
   </si>
   <si>
     <t>be-model-medicationprescription.dispenseRequest.id</t>
@@ -531,6 +528,12 @@
   </si>
   <si>
     <t>Instructions for reimbursement</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>MedicationRequestReimbursementTypeVS</t>
   </si>
   <si>
     <t>be-model-medicationprescription.groupIdentifier</t>
@@ -934,8 +937,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="19.625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="29.6328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="40.16796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1391,7 +1394,7 @@
         <v>88</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1459,10 +1462,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1485,13 +1488,13 @@
         <v>74</v>
       </c>
       <c r="K6" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="L6" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L6" t="s" s="2">
-        <v>92</v>
-      </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1542,7 +1545,7 @@
         <v>74</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>80</v>
@@ -1559,10 +1562,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1585,13 +1588,13 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L7" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="L7" t="s" s="2">
-        <v>95</v>
-      </c>
       <c r="M7" t="s" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1642,7 +1645,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1659,10 +1662,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1685,13 +1688,13 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>97</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>98</v>
-      </c>
-      <c r="M8" t="s" s="2">
-        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1742,7 +1745,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1759,10 +1762,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1785,13 +1788,13 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="L9" t="s" s="2">
-        <v>102</v>
-      </c>
       <c r="M9" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1842,7 +1845,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1859,10 +1862,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1885,13 +1888,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L10" t="s" s="2">
         <v>104</v>
       </c>
-      <c r="L10" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1942,7 +1945,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -1954,15 +1957,15 @@
         <v>74</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1985,13 +1988,13 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L11" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L11" t="s" s="2">
+      <c r="M11" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2042,7 +2045,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2059,14 +2062,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -2085,16 +2088,16 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2132,19 +2135,19 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AC12" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AC12" t="s" s="2">
+      <c r="AD12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE12" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AD12" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE12" t="s" s="2">
+      <c r="AF12" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2156,19 +2159,19 @@
         <v>74</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2181,25 +2184,25 @@
         <v>74</v>
       </c>
       <c r="I13" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="J13" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="K13" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="J13" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="K13" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O13" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O13" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>74</v>
@@ -2248,7 +2251,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2260,15 +2263,15 @@
         <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2291,13 +2294,13 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2348,7 +2351,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2365,10 +2368,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2391,13 +2394,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2448,7 +2451,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2465,10 +2468,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2491,13 +2494,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L16" t="s" s="2">
-        <v>134</v>
-      </c>
       <c r="M16" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2548,7 +2551,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2565,10 +2568,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2591,13 +2594,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>136</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>137</v>
-      </c>
       <c r="M17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2648,7 +2651,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2665,10 +2668,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2691,13 +2694,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L18" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="M18" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2748,7 +2751,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2765,10 +2768,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2791,13 +2794,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2848,7 +2851,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -2865,10 +2868,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2891,13 +2894,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>145</v>
-      </c>
       <c r="M20" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2948,7 +2951,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>75</v>
@@ -2965,10 +2968,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2991,13 +2994,13 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3048,7 +3051,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3065,10 +3068,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3091,13 +3094,13 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3148,7 +3151,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3165,10 +3168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3191,13 +3194,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3248,7 +3251,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3265,10 +3268,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3291,13 +3294,13 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3348,7 +3351,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3360,15 +3363,15 @@
         <v>74</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3391,13 +3394,13 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3448,7 +3451,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3465,14 +3468,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3491,16 +3494,16 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -3538,19 +3541,19 @@
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AC26" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AC26" t="s" s="2">
+      <c r="AD26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE26" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AD26" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE26" t="s" s="2">
+      <c r="AF26" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AF26" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3562,19 +3565,19 @@
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -3587,25 +3590,25 @@
         <v>74</v>
       </c>
       <c r="I27" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="J27" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="K27" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>74</v>
@@ -3654,7 +3657,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3666,15 +3669,15 @@
         <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3697,13 +3700,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="L28" t="s" s="2">
-        <v>159</v>
-      </c>
       <c r="M28" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3754,7 +3757,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3771,10 +3774,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3797,13 +3800,13 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>162</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3854,7 +3857,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -3871,10 +3874,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3897,13 +3900,13 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3930,13 +3933,13 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
+        <v>164</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -3954,7 +3957,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -3971,10 +3974,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4000,10 +4003,10 @@
         <v>81</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4054,7 +4057,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4071,10 +4074,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4097,13 +4100,13 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4154,7 +4157,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4171,10 +4174,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4197,13 +4200,13 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4254,7 +4257,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4271,10 +4274,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4297,13 +4300,13 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4354,7 +4357,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4371,10 +4374,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4397,13 +4400,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4454,7 +4457,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -4466,15 +4469,15 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4497,13 +4500,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>109</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>110</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4554,7 +4557,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -4571,14 +4574,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -4597,16 +4600,16 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>115</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4644,19 +4647,19 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="AC37" t="s" s="2">
         <v>118</v>
       </c>
-      <c r="AC37" t="s" s="2">
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="AD37" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE37" t="s" s="2">
+      <c r="AF37" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -4668,19 +4671,19 @@
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -4693,25 +4696,25 @@
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="J38" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="K38" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>127</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>128</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -4760,7 +4763,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -4772,15 +4775,15 @@
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4803,13 +4806,13 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4860,7 +4863,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -4877,10 +4880,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4903,13 +4906,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4960,7 +4963,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -4977,10 +4980,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5003,13 +5006,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5060,7 +5063,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5077,10 +5080,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5103,13 +5106,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5160,7 +5163,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>

--- a/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
+++ b/branches/prescription/StructureDefinition-be-model-medicationprescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T16:05:52+00:00</t>
+    <t>2024-10-22T10:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
